--- a/Data Files/Auto/RecusaDeFrotaData/RecusaDeFrota.xlsx
+++ b/Data Files/Auto/RecusaDeFrotaData/RecusaDeFrota.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24931"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ\Data Files\Auto\RecusaDeFrotaData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49084B3E-CB72-4A2A-B090-0B1673D74BD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95EE6388-8EB8-41A3-A185-1AC29B871890}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="12600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RecusaDeFrota" sheetId="2" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="9">
   <si>
     <t>Fluxo</t>
   </si>
@@ -52,10 +52,10 @@
     <t>x</t>
   </si>
   <si>
-    <t>Prezados, renovações Externas e Seguro Novo devem ser cotados exclusivamente na ponta via Cotador considerando o mínimo de 3 e máximo de 60 itens. Ressaltamos que a condição válida é aquela apresentada pelo Cotador, não atuamos com repique nem aceitações especiais para esse segmento.              Frotas acima de 60 itens optamos por não entrar na concorrência. Fique atento no preenchimento do campo Tipo de Seguro do fluxo. Caso seja uma Renovação Interna, orientamos abrir novo fluxo com o campo Tipo de Seguro preenchido corretamente para possamos atuar na sua solicitação.                  Atenciosamente,                                                                                                                                                                                                          Frota Auto Allianz</t>
-  </si>
-  <si>
     <t>geral</t>
+  </si>
+  <si>
+    <t>Prezados, Renovações Externas e Seguro Novo devem ser cotados exclusivamente na ponta via Cotador considerando  o mínimo de 3 e máximo de 60 itens. Frotas acima de 60 itens optamos por não entrar na concorrência. Fique atento no preenchimento do campo Tipo de Seguro do fluxo. Caso seja uma Renovação Interna, orientamos abrir novo fluxo com o campo Tipo de Seguro preenchido corretamente para possamos atuar na sua solicitação. Em caso de dúvidas, procure seu account para orientações.</t>
   </si>
 </sst>
 </file>
@@ -128,7 +128,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -158,32 +158,6 @@
       <right style="hair">
         <color auto="1"/>
       </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color auto="1"/>
-      </left>
-      <right style="hair">
-        <color auto="1"/>
-      </right>
-      <top style="hair">
-        <color auto="1"/>
-      </top>
-      <bottom style="hair">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color auto="1"/>
-      </left>
-      <right style="hair">
-        <color auto="1"/>
-      </right>
       <top style="hair">
         <color auto="1"/>
       </top>
@@ -198,7 +172,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -223,15 +197,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -553,7 +522,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.28515625" style="4" customWidth="1" collapsed="1"/>
@@ -586,14 +555,14 @@
       </c>
     </row>
     <row r="2" spans="1:6" s="8" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A2" s="13">
-        <v>717344</v>
-      </c>
-      <c r="B2" s="14" t="s">
+      <c r="A2" s="10">
+        <v>774986</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="11" t="s">
         <v>8</v>
-      </c>
-      <c r="C2" s="15" t="s">
-        <v>7</v>
       </c>
       <c r="D2" s="9" t="s">
         <v>6</v>
@@ -602,14 +571,14 @@
       <c r="F2" s="7"/>
     </row>
     <row r="3" spans="1:6" s="8" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A3" s="13">
-        <v>717345</v>
-      </c>
-      <c r="B3" s="14" t="s">
+      <c r="A3" s="10">
+        <v>775010</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="11" t="s">
         <v>8</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>7</v>
       </c>
       <c r="D3" s="9" t="s">
         <v>6</v>
@@ -618,14 +587,14 @@
       <c r="F3" s="7"/>
     </row>
     <row r="4" spans="1:6" s="8" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A4" s="13">
-        <v>717403</v>
-      </c>
-      <c r="B4" s="14" t="s">
+      <c r="A4" s="10">
+        <v>775016</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="11" t="s">
         <v>8</v>
-      </c>
-      <c r="C4" s="15" t="s">
-        <v>7</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>6</v>
@@ -633,421 +602,71 @@
       <c r="E4" s="7"/>
       <c r="F4" s="7"/>
     </row>
-    <row r="5" spans="1:6" s="8" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A5" s="16">
-        <v>717464</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-    </row>
-    <row r="6" spans="1:6" s="8" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A6" s="13">
-        <v>717353</v>
-      </c>
-      <c r="B6" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-    </row>
-    <row r="7" spans="1:6" s="8" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A7" s="13">
-        <v>717363</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-    </row>
-    <row r="8" spans="1:6" s="8" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A8" s="13">
-        <v>717446</v>
-      </c>
-      <c r="B8" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-    </row>
-    <row r="9" spans="1:6" s="8" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A9" s="13">
-        <v>717455</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="6"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="11"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="6"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="11"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="6"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="11"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="6"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="11"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="6"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="11"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="13">
-        <v>717492</v>
-      </c>
-      <c r="B10" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
+      <c r="A10" s="6"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="11"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="13">
-        <v>717372</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
+      <c r="C11" s="11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="13">
-        <v>717529</v>
-      </c>
-      <c r="B12" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
+      <c r="C12" s="11"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="10">
-        <v>717589</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
+      <c r="C13" s="11"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="10">
-        <v>717598</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
+      <c r="C14" s="11"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="10">
-        <v>717602</v>
-      </c>
-      <c r="B15" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
+      <c r="C15" s="11"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="10">
-        <v>717639</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="10">
-        <v>717669</v>
-      </c>
-      <c r="B17" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="10">
-        <v>717720</v>
-      </c>
-      <c r="B18" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="10">
-        <v>717736</v>
-      </c>
-      <c r="B19" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="10">
-        <v>717538</v>
-      </c>
-      <c r="B20" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="10">
-        <v>717771</v>
-      </c>
-      <c r="B21" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="10"/>
-      <c r="B22" s="11"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="10"/>
-      <c r="B23" s="11"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="10"/>
-      <c r="B24" s="11"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="10"/>
-      <c r="B25" s="11"/>
-      <c r="C25" s="12"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="10"/>
-      <c r="B26" s="11"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="10"/>
-      <c r="B27" s="11"/>
-      <c r="C27" s="12"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="7"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="10"/>
-      <c r="B28" s="11"/>
-      <c r="C28" s="12"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="10"/>
-      <c r="B29" s="11"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="7"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="10"/>
-      <c r="B30" s="11"/>
-      <c r="C30" s="12"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="7"/>
-      <c r="F30" s="7"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="10"/>
-      <c r="B31" s="11"/>
-      <c r="C31" s="12"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="10"/>
-      <c r="B32" s="11"/>
-      <c r="C32" s="12"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="7"/>
-      <c r="F32" s="7"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="10"/>
-      <c r="B33" s="11"/>
-      <c r="C33" s="12"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="7"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="10"/>
-      <c r="B34" s="11"/>
-      <c r="C34" s="12"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="7"/>
-      <c r="F34" s="7"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="10"/>
-      <c r="B35" s="11"/>
-      <c r="C35" s="12"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="7"/>
-      <c r="F35" s="7"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="10"/>
-      <c r="B36" s="11"/>
-      <c r="C36" s="12"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="7"/>
-      <c r="F36" s="7"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="10"/>
-      <c r="B37" s="11"/>
-      <c r="C37" s="12"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="7"/>
-      <c r="F37" s="7"/>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E38" s="7"/>
-      <c r="F38" s="7"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E39" s="7"/>
-      <c r="F39" s="7"/>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E40" s="7"/>
-      <c r="F40" s="7"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E41" s="7"/>
-      <c r="F41" s="7"/>
+      <c r="C16" s="11"/>
+    </row>
+    <row r="17" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C17" s="11"/>
+    </row>
+    <row r="18" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C18" s="11"/>
+    </row>
+    <row r="19" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C19" s="11"/>
+    </row>
+    <row r="20" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C20" s="11"/>
+    </row>
+    <row r="21" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C21" s="11"/>
+    </row>
+    <row r="22" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C22" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
